--- a/jogos_2025-02-07.xlsx
+++ b/jogos_2025-02-07.xlsx
@@ -633,26 +633,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -669,65 +669,65 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.72</v>
+        <v>3.19</v>
       </c>
       <c r="N2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.05</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.14</v>
+        <v>3.34</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['13', '51', '65', '72', '78']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45695.22916666666</v>
@@ -762,26 +762,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>3.19</v>
+        <v>3.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>2.38</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.34</v>
+        <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['13', '51', '65', '72', '78']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45695.22916666666</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,34 +2088,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
         <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2127,26 +2127,26 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45695.41666666666</v>
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.67</v>
       </c>
-      <c r="O14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['22', '89']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45695.41666666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,34 +2346,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2385,31 +2385,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '69']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2422,7 +2422,7 @@
         <v>1.73</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45695.41666666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,34 +2475,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
         <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
         <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2514,26 +2514,26 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45695.41666666666</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2604,34 +2604,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2655,19 +2655,19 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['45+4', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['22', '89']</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45695.41666666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,16 +3223,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aqaba</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>5.75</v>
+        <v>2.82</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>2.61</v>
       </c>
       <c r="O22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.57</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>2.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.56</v>
+        <v>1.36</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>5.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG22" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.17</v>
+        <v>2.23</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45695.45833333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Aqaba</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['34', '44', '63']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45695.45833333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.11</v>
+        <v>3.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>3.73</v>
+        <v>4.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="X25" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.77</v>
+        <v>3.28</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+12']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45695.45833333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Katsina United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Heartland</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.57</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.25</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="AD26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>4.75</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['90+12']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45695.45833333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,65 +3894,65 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="M27" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="O27" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="X27" t="n">
-        <v>2.15</v>
+        <v>3.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.89</v>
+        <v>2.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.45</v>
+        <v>3.77</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45695.45833333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Katsina United</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Heartland</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>8.08</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.65</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AA28" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['34', '44', '63']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45695.45833333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.95</v>
+        <v>6.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
         <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="X36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['18', '90+9']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['22', '29']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.93</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="M37" t="n">
-        <v>2.82</v>
+        <v>6.25</v>
       </c>
       <c r="N37" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="P37" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>2.06</v>
+        <v>4.33</v>
       </c>
       <c r="T37" t="n">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="U37" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="V37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>2.15</v>
+        <v>6.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.9</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.08</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
+          <t>['17', '62']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG37" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.69</v>
+        <v>3.95</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5302,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N38" t="n">
-        <v>5.3</v>
+        <v>6.53</v>
       </c>
       <c r="O38" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['3', '7']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>3.1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['18', '90+9']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5434,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>2.31</v>
+        <v>3.6</v>
       </c>
       <c r="P39" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.4</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.94</v>
+        <v>1.49</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.22</v>
       </c>
-      <c r="M40" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="N40" t="n">
-        <v>10</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="X40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['22', '29']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.93</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['17', '62']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>3.7</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Šibenik</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,65 +5700,65 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>7.31</v>
       </c>
       <c r="N41" t="n">
-        <v>6.53</v>
+        <v>11.95</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="P41" t="n">
-        <v>2.45</v>
+        <v>3.01</v>
       </c>
       <c r="Q41" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Y41" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AD41" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['3', '7']</t>
+          <t>['38', '74', '78']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Šibenik</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5829,65 +5829,65 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>7.31</v>
+        <v>2.82</v>
       </c>
       <c r="N42" t="n">
-        <v>11.95</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>10.71</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="S42" t="n">
-        <v>3.8</v>
+        <v>2.06</v>
       </c>
       <c r="T42" t="n">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="X42" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.47</v>
+        <v>2.9</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['38', '74', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH42" t="n">
-        <v>5</v>
+        <v>1.69</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AJ42" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45695.58333333334</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI43" t="n">
         <v>1.57</v>
       </c>
-      <c r="S43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ43" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45695.58333333334</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>4.8</v>
+        <v>2.87</v>
       </c>
       <c r="O44" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.22</v>
       </c>
-      <c r="X44" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC44" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['31', '37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45695.60416666666</v>
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.95</v>
       </c>
-      <c r="P46" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U46" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V46" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W46" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X46" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
+          <t>['42', '60']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
       <c r="AG46" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45695.60416666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z47" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA47" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['42', '60']</t>
+          <t>['31', '37']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45695.60416666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandhausen</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.95</v>
+        <v>4.44</v>
       </c>
       <c r="R49" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T49" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X49" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Z49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA49" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45695.625</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Sandhausen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z51" t="n">
         <v>1.91</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U51" t="n">
+      <c r="AA51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.36</v>
       </c>
-      <c r="V51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC51" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
       <c r="AG51" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45695.625</v>
@@ -7093,91 +7093,91 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q52" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S52" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T52" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="U52" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W52" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X52" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Y52" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['24', '27']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.74</v>
       </c>
-      <c r="AH52" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI52" t="n">
-        <v>2.53</v>
+        <v>1.66</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45695.64583333334</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Schaffhausen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="M53" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="O53" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="P53" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q53" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T53" t="n">
         <v>3.32</v>
       </c>
-      <c r="R53" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.66</v>
-      </c>
       <c r="U53" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="X53" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7311,20 +7311,20 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45695.64583333334</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,25 +7480,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FC Schaffhausen</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="N55" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="P55" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="R55" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T55" t="n">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="U55" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V55" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="X55" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="Y55" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ55" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45695.64583333334</v>
@@ -7738,22 +7738,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="M57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T57" t="n">
         <v>3.1</v>
       </c>
-      <c r="N57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.32</v>
-      </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V57" t="n">
         <v>1.02</v>
       </c>
       <c r="W57" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X57" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AA57" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
+          <t>['24', '27']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH57" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH57" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AI57" t="n">
-        <v>1.69</v>
+        <v>2.53</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45695.64583333334</v>
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="O58" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="R58" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S58" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T58" t="n">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="U58" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W58" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X58" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45695.64583333334</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>3.77</v>
       </c>
       <c r="N59" t="n">
-        <v>3.28</v>
+        <v>3.97</v>
       </c>
       <c r="O59" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S59" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="T59" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U59" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V59" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X59" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AC59" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>['29', '69']</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH59" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AI59" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45695.66666666666</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,87 +8125,87 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KMSK Deinze</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8214,20 +8214,20 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['15', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45695.66666666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Riadi Salmi</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chabab Mohammedia</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="O61" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="R61" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S61" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="T61" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U61" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V61" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X61" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>['29', '77']</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
         <v>1.31</v>
       </c>
-      <c r="X61" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH61" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AJ61" t="n">
-        <v>4.33</v>
+        <v>2.23</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45695.66666666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,109 +8512,109 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>2</v>
       </c>
-      <c r="J63" t="n">
-        <v>1</v>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.66</v>
+        <v>4.33</v>
       </c>
       <c r="M63" t="n">
-        <v>4.19</v>
+        <v>3.53</v>
       </c>
       <c r="N63" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="O63" t="n">
-        <v>2.2</v>
+        <v>4.75</v>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R63" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S63" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T63" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="U63" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X63" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>['12', '27']</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AJ63" t="n">
         <v>1.62</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X63" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>['1', '45+1', '79']</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>['20', '50', '86']</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45695.66666666666</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T64" t="n">
         <v>2.8</v>
       </c>
-      <c r="O64" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S64" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U64" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W64" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X64" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['29', '77']</t>
+          <t>['15', '88']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45695.66666666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Riadi Salmi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Chabab Mohammedia</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="N65" t="n">
-        <v>3.53</v>
+        <v>6.5</v>
       </c>
       <c r="O65" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P65" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T65" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U65" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V65" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W65" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X65" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45695.66666666666</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,22 +8899,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="N66" t="n">
-        <v>3.97</v>
+        <v>4.6</v>
       </c>
       <c r="O66" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="P66" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S66" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T66" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U66" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V66" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W66" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X66" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="Z66" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>['28', '49', '75']</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH66" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA66" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>['29', '69']</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI66" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45695.66666666666</v>
@@ -9028,25 +9028,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,28 +9054,28 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.33</v>
+        <v>2.06</v>
       </c>
       <c r="M67" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N67" t="n">
         <v>3.53</v>
       </c>
-      <c r="N67" t="n">
-        <v>1.79</v>
-      </c>
       <c r="O67" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="P67" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="R67" t="n">
         <v>1.4</v>
       </c>
       <c r="S67" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T67" t="n">
         <v>2.8</v>
@@ -9105,32 +9105,32 @@
         <v>1.28</v>
       </c>
       <c r="AC67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI67" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['12', '27']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45695.66666666666</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,19 +9157,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -9183,80 +9183,80 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N68" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="O68" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P68" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="R68" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S68" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y68" t="n">
         <v>2.1</v>
       </c>
-      <c r="U68" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X68" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z68" t="n">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ68" t="n">
         <v>2.4</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,22 +9286,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G69" t="n">
         <v>3</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="M69" t="n">
-        <v>3.76</v>
+        <v>4.19</v>
       </c>
       <c r="N69" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P69" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q69" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X69" t="n">
         <v>5</v>
       </c>
-      <c r="R69" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T69" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U69" t="n">
+      <c r="Y69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>['1', '45+1', '79']</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>['20', '50', '86']</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI69" t="n">
         <v>1.44</v>
       </c>
-      <c r="V69" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X69" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>['28', '49', '75']</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ69" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45695.66666666666</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,16 +9544,16 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KMSK Deinze</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -9566,87 +9566,87 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45695.66666666666</v>
@@ -9802,22 +9802,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G73" t="n">
         <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="N73" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="O73" t="n">
-        <v>2.36</v>
+        <v>2.99</v>
       </c>
       <c r="P73" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R73" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S73" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="T73" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U73" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="V73" t="n">
         <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X73" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="AB73" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC73" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1.53</v>
       </c>
       <c r="AD73" t="n">
         <v>2.32</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['36', '63']</t>
+          <t>['2', '10']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['50', '57', '67', '72']</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.81</v>
+        <v>1.47</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45695.67708333334</v>
@@ -9931,22 +9931,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -9957,83 +9957,83 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="M74" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="N74" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="O74" t="n">
-        <v>2.99</v>
+        <v>2.36</v>
       </c>
       <c r="P74" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R74" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S74" t="n">
-        <v>3.26</v>
+        <v>3.46</v>
       </c>
       <c r="T74" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U74" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="V74" t="n">
         <v>1.01</v>
       </c>
       <c r="W74" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X74" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AD74" t="n">
         <v>2.32</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>['2', '10']</t>
+          <t>['36', '63']</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>['50', '57', '67', '72']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="AJ74" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45695.67708333334</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,25 +10060,25 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -10086,83 +10086,83 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="M75" t="n">
-        <v>3.25</v>
+        <v>3.76</v>
       </c>
       <c r="N75" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O75" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T75" t="n">
         <v>2.5</v>
       </c>
-      <c r="P75" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>4</v>
-      </c>
-      <c r="R75" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S75" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T75" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U75" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V75" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W75" t="n">
         <v>1.25</v>
       </c>
       <c r="X75" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD75" t="n">
         <v>2.1</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>['29', '60']</t>
+          <t>['8', '48', '61']</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>['37', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45695.6875</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,25 +10189,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -10215,83 +10215,83 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="M76" t="n">
-        <v>13</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="O76" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="P76" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S76" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="T76" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W76" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="X76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Z76" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['56', '82', '90+7']</t>
+          <t>['29', '60']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '74']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="AH76" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AJ76" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45695.6875</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,25 +10318,25 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -10344,83 +10344,83 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="M77" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="N77" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="O77" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P77" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R77" t="n">
         <v>1.5</v>
       </c>
       <c r="S77" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T77" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U77" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W77" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X77" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA77" t="n">
-        <v>3.95</v>
+        <v>4.83</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC77" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AJ77" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45695.6875</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,22 +10447,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10473,65 +10473,65 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.81</v>
+        <v>2.49</v>
       </c>
       <c r="M78" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>3.06</v>
       </c>
       <c r="O78" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="P78" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R78" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S78" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="T78" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U78" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V78" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W78" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X78" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB78" t="n">
         <v>1.25</v>
       </c>
-      <c r="X78" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC78" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['8', '48', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -10540,16 +10540,16 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AJ78" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45695.6875</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,25 +10576,25 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -10602,83 +10602,83 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="N79" t="n">
-        <v>3.9</v>
+        <v>19</v>
       </c>
       <c r="O79" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="P79" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>12</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC79" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q79" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T79" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB79" t="n">
+      <c r="AD79" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>['56', '82', '90+7']</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI79" t="n">
         <v>1.17</v>
       </c>
-      <c r="AC79" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>['38']</t>
-        </is>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ79" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45695.6875</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,25 +10705,25 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -10731,83 +10731,83 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P80" t="n">
         <v>1.91</v>
       </c>
-      <c r="M80" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O80" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P80" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q80" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="R80" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S80" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T80" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U80" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V80" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W80" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X80" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Y80" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA80" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>45695.6875</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -10860,83 +10860,83 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="N81" t="n">
-        <v>3.26</v>
+        <v>2.81</v>
       </c>
       <c r="O81" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S81" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T81" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U81" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W81" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="X81" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Y81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ81" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>['46', '58']</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AG81" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45695.6875</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,25 +10963,25 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -10989,83 +10989,83 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="M82" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="O82" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P82" t="n">
         <v>2</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R82" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S82" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X82" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>['46', '58']</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ82" t="n">
         <v>2.4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U82" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W82" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X82" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AG82" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK82" s="3" t="n">
         <v>45695.6875</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,22 +11092,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -11118,22 +11118,22 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="M83" t="n">
         <v>3.12</v>
       </c>
       <c r="N83" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="O83" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P83" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R83" t="n">
         <v>1.5</v>
@@ -11142,10 +11142,10 @@
         <v>2.5</v>
       </c>
       <c r="T83" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U83" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V83" t="n">
         <v>1.01</v>
@@ -11157,10 +11157,10 @@
         <v>2.85</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA83" t="n">
         <v>3.95</v>
@@ -11169,32 +11169,32 @@
         <v>1.22</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ83" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK83" s="3" t="n">
         <v>45695.6875</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,16 +11221,16 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -11247,22 +11247,22 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N84" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="O84" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="P84" t="n">
         <v>2.05</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R84" t="n">
         <v>1.44</v>
@@ -11277,13 +11277,13 @@
         <v>1.33</v>
       </c>
       <c r="V84" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W84" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X84" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Y84" t="n">
         <v>2</v>
@@ -11292,38 +11292,38 @@
         <v>1.65</v>
       </c>
       <c r="AA84" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC84" t="n">
         <v>1.91</v>
       </c>
       <c r="AD84" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG84" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>45695.6875</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,25 +11479,25 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -11505,83 +11505,83 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.57</v>
+        <v>1.6</v>
       </c>
       <c r="M86" t="n">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="N86" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="O86" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="P86" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S86" t="n">
         <v>2.75</v>
       </c>
-      <c r="R86" t="n">
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X86" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI86" t="n">
         <v>1.44</v>
       </c>
-      <c r="S86" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T86" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U86" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V86" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W86" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X86" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD86" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>['34', '89']</t>
-        </is>
-      </c>
-      <c r="AG86" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH86" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI86" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AJ86" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AK86" s="3" t="n">
         <v>45695.69791666666</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,16 +11608,16 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>2</v>
@@ -11634,83 +11634,83 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>6</v>
+        <v>3.57</v>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>3.37</v>
       </c>
       <c r="N87" t="n">
-        <v>1.42</v>
+        <v>2.18</v>
       </c>
       <c r="O87" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="P87" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="R87" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S87" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T87" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V87" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W87" t="n">
         <v>1.36</v>
       </c>
-      <c r="S87" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V87" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W87" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X87" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AA87" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB87" t="n">
         <v>1.28</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>['25', '90+1']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>['12', '90+10']</t>
+          <t>['34', '89']</t>
         </is>
       </c>
       <c r="AG87" t="n">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AI87" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="AJ87" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AK87" s="3" t="n">
         <v>45695.69791666666</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,25 +11737,25 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G88" t="n">
         <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -11763,83 +11763,83 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.58</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N88" t="n">
-        <v>4.6</v>
+        <v>1.42</v>
       </c>
       <c r="O88" t="n">
-        <v>2.01</v>
+        <v>5.5</v>
       </c>
       <c r="P88" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.25</v>
+        <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S88" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T88" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U88" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="V88" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W88" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="X88" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>['52', '76']</t>
+          <t>['25', '90+1']</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '90+10']</t>
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>1.11</v>
+        <v>2.65</v>
       </c>
       <c r="AH88" t="n">
-        <v>2.35</v>
+        <v>1.07</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.41</v>
+        <v>3.75</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="AK88" s="3" t="n">
         <v>45695.69791666666</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,19 +11866,19 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -11892,83 +11892,83 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M89" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N89" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P89" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q89" t="n">
         <v>5.25</v>
       </c>
-      <c r="O89" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P89" t="n">
+      <c r="R89" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X89" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z89" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q89" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S89" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T89" t="n">
-        <v>3</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V89" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W89" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X89" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AA89" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
+          <t>['52', '76']</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
       <c r="AG89" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH89" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AJ89" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AK89" s="3" t="n">
         <v>45695.69791666666</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,25 +12640,25 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Cerro Largo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -12666,34 +12666,34 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="N95" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O95" t="n">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="P95" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.6</v>
+        <v>4.86</v>
       </c>
       <c r="R95" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S95" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="T95" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U95" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="V95" t="n">
         <v>1.1</v>
@@ -12702,47 +12702,47 @@
         <v>1.61</v>
       </c>
       <c r="X95" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Y95" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA95" t="n">
-        <v>6</v>
+        <v>4.53</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '32', '33', '59']</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>['40', '85']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AI95" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AJ95" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AK95" s="3" t="n">
         <v>45695.79166666666</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,60 +12769,60 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M96" t="n">
         <v>3</v>
       </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="M96" t="n">
-        <v>3.06</v>
-      </c>
       <c r="N96" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O96" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="P96" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="R96" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S96" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="T96" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U96" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="V96" t="n">
         <v>1.1</v>
@@ -12831,47 +12831,47 @@
         <v>1.61</v>
       </c>
       <c r="X96" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.53</v>
+        <v>6</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AD96" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>['6', '32', '33', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['40', '85']</t>
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AJ96" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AK96" s="3" t="n">
         <v>45695.79166666666</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,83 +12924,83 @@
         </is>
       </c>
       <c r="L97" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O97" t="n">
+        <v>3</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S97" t="n">
         <v>2.2</v>
       </c>
-      <c r="M97" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N97" t="n">
+      <c r="T97" t="n">
         <v>4</v>
       </c>
-      <c r="O97" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P97" t="n">
+      <c r="U97" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X97" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>['36', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG97" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI97" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q97" t="n">
-        <v>5</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S97" t="n">
-        <v>2</v>
-      </c>
-      <c r="T97" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V97" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W97" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X97" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>['17', '83']</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG97" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH97" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI97" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AJ97" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AK97" s="3" t="n">
         <v>45695.83333333334</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,65 +13053,65 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N98" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P98" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="S98" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T98" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U98" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V98" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W98" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="X98" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AA98" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>['36', '90+6']</t>
+          <t>['17', '83']</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -13120,16 +13120,16 @@
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AI98" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AJ98" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AK98" s="3" t="n">
         <v>45695.83333333334</v>
@@ -13414,25 +13414,25 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M101" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N101" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O101" t="n">
         <v>4</v>
@@ -13455,28 +13455,28 @@
         <v>1.83</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R101" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X101" t="n">
         <v>2.2</v>
-      </c>
-      <c r="T101" t="n">
-        <v>4</v>
-      </c>
-      <c r="U101" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V101" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W101" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X101" t="n">
-        <v>2.37</v>
       </c>
       <c r="Y101" t="n">
         <v>2.88</v>
@@ -13485,10 +13485,10 @@
         <v>1.4</v>
       </c>
       <c r="AA101" t="n">
-        <v>6.23</v>
+        <v>6.32</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC101" t="n">
         <v>2.25</v>
@@ -13498,25 +13498,25 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>['80', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>['58', '81']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG101" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AI101" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ101" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AK101" s="3" t="n">
         <v>45695.92708333334</v>
@@ -13543,25 +13543,25 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M102" t="n">
         <v>3.1</v>
       </c>
-      <c r="M102" t="n">
-        <v>2.88</v>
-      </c>
       <c r="N102" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O102" t="n">
         <v>4</v>
@@ -13584,28 +13584,28 @@
         <v>1.83</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R102" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S102" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T102" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U102" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V102" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W102" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="X102" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Y102" t="n">
         <v>2.88</v>
@@ -13614,10 +13614,10 @@
         <v>1.4</v>
       </c>
       <c r="AA102" t="n">
-        <v>6.32</v>
+        <v>6.23</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC102" t="n">
         <v>2.25</v>
@@ -13627,25 +13627,25 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80', '83']</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['58', '81']</t>
         </is>
       </c>
       <c r="AG102" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI102" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ102" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AK102" s="3" t="n">
         <v>45695.92708333334</v>
